--- a/5_Snowballing/Merged_Studies_3.xlsx
+++ b/5_Snowballing/Merged_Studies_3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antoniotrovato/Documents/GitHub/RegressionTestingOptimizationSLR/5_Snowballing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1CF7CE1-7C75-B54E-B3B2-7647D618A2D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FE1046-3881-774E-AE38-ECE683493F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="10000" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="10000" windowHeight="15560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="1304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1735" uniqueCount="1292">
   <si>
     <t>ID</t>
   </si>
@@ -2955,15 +2955,6 @@
   </si>
   <si>
     <t>Test-case prioritization, proposed at the end of last century, aims to schedule the execution order of test cases so as to improve test effectiveness. In the past years, test-case prioritization has gained much attention, and has significant achievements in five aspects: prioritization algorithms, coverage criteria, measurement, practical concerns involved, and application scenarios. In this article, we will first review the achievements of test-case prioritization from these five aspects and then give our perspectives on its challenges.</t>
-  </si>
-  <si>
-    <t>R Mukherjee, KS Patnaik</t>
-  </si>
-  <si>
-    <t>Journal of King Saud University-Computer and Information Sciences, 2021</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> A survey on different approaches for software test case prioritization</t>
   </si>
   <si>
     <t>O Dahiya, K Solanki</t>
@@ -3011,12 +3002,6 @@
 The solution delivers optimal results in pseudo-polynomial time complexity, is effective for amounts of test cases up to the order of millions and compared with the classical dynamic programming methods leads to higher number of test cases to be involved in the selection process due to reduced memory consumption.</t>
   </si>
   <si>
-    <t>MJ Arafeen, H Do</t>
-  </si>
-  <si>
-    <t>Test case prioritization using requirements-based clustering</t>
-  </si>
-  <si>
     <t>Christopher Henard, Mike Papadakis, Mark Harman, Yue Jia, Yves Le Traon</t>
   </si>
   <si>
@@ -3066,19 +3051,6 @@
 Regression test case selection techniques attempt to increase the testing effectiveness based on the measurement capabilities, such as cost, coverage, and fault detection. This systematic literature review presents state-of-the-art research in effective regression test case selection techniques. We examined 47 empirical studies published between 2007 and 2015. The selected studies are categorized according to the selection procedure, empirical study design, and adequacy criteria with respect to their effectiveness measurement capability and methods used to measure the validity of these results.
 The results showed that mining and learning-based regression test case selection was reported in 39% of the studies, unit level testing was reported in 18% of the studies, and object-oriented environment (Java) was used in 26% of the studies. Structural faults, the most common target, was used in 55% of the studies. Overall, only 39% of the studies conducted followed experimental guidelines and are reproducible.
 There are 7 different cost measures, 13 different coverage types, and 5 fault-detection metrics reported in these studies. It is also observed that 70% of the studies being analyzed used cost as the effectiveness measure compared to 31% that used fault-detection capability and 16% that used coverage.</t>
-  </si>
-  <si>
-    <t>A Choudhary, AP Agrawal, A Kaur</t>
-  </si>
-  <si>
-    <t>Proceedings of the 11th International Workshop on Search-Based Software Testing, 2018</t>
-  </si>
-  <si>
-    <t>An effective approach for regression test case selection using pareto based multi-objective harmony search</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Regression testing is a way of catching bugs in new builds and releases to avoid the product risks. Corrective, progressive, retest all and selective regression testing are strategies to perform regression testing. Retesting all existing test cases is one of the most reliable approaches but it is costly in terms of time and effort. This limitation opened a scope to optimize regression testing cost by selecting only a subset of test cases that can detect faults in optimal time and effort. This paper proposes Pareto based Multi-Objective Harmony Search approach for regression test case selection from an existing test suite to achieve some test adequacy criteria. Fault coverage, unique faults covered and algorithm execution time are utilised as performance measures to achieve optimization criteria. The performance evaluation of proposed approach is performed against Bat Search and Cuckoo Search optimization. The results of statistical tests indicate significant improvement over existing approaches.</t>
   </si>
   <si>
     <t>DK Yadav, S Dutta</t>
@@ -3215,30 +3187,6 @@
   </si>
   <si>
     <t>Modified source code validation is done by regression testing. In regression testing, the time and resources are limited, in which we have to select the minimal test cases from test suites to reduce execution time. The test case minimization process deals with the optimization of the regression testing by removing redundant test cases or prioritizing the test cases. This study proposed a test case prioritization approach based on multiobjective particle swarm optimization (MOPSO) by considering minimum execution time, maximum fault detection ability, and maximum code coverage. The MOPSO algorithm is used for the prioritization of test cases with parameters including execution time, fault detection ability, and code coverage. Three datasets are selected to evaluate the proposed MOPSO technique including TreeDataStructure, JodaTime, and Triangle. The proposed MOPSO is compared with the no ordering, reverse ordering, and random ordering technique for evaluating the effectiveness. The higher values of results represent the more effectiveness and the efficiency of the proposed MOPSO as compared to other approaches for TreeDataStructure, JodaTime, and Triangle datasets. The result is presented to 100‐index mode relevant from low to high values; after that, test cases are prioritized. The experiment is conducted on three open‐source java applications and evaluated using metrics inclusiveness, precision, and size reduction of a matrix of the test suite. The results revealed that all scenarios performed well in acceptable mode, and the technique is 17% to 86% more effective in terms of inclusiveness, 33% to 85% more effective in terms of precision, and 17% minimum to 86% maximum in size reduction of metrics.</t>
-  </si>
-  <si>
-    <t>Jianlei Chia, Yu Quc, Qinghua Zhenga, Zijiang Yangb, Wuxia Jina, Di Cuia, Ting Liua</t>
-  </si>
-  <si>
-    <t>The Journal of Systems and Software</t>
-  </si>
-  <si>
-    <t>Test case prioritization (TCP), which aims at detecting faults as early as possible is broadly used in pro-
-gram regression testing. Most existing TCP techniques exploit coverage information with the hypothesis
-that higher coverage has more chance to catch bugs. Static structure information such as function and
-statement are frequently employed as coverage granularity. However, the former consumes less costs but
-presents lower capability to detect faults, the latter typically incurs more overhead.
-In this paper, dynamic function call sequences are argued that can guide TCP effectively. Same set of func-
-tions/statements can exhibit very different execution behaviors. Therefore, mapping program behaviors
-to unit-based (function/statement) coverage may not be enough to predict fault detection capability. We
-propose a new approach AGC (Additional Greedy method Call sequence). Our approach leverages dynamic
-relation-based coverage as measurement to extend the original additional greedy coverage algorithm in
-TCP techniques.
-We conduct our experiments on eight real-world java open source projects and systematically compare
-AGC against 22 state-of-the-art TCP techniques with different granularities. Results show that AGC out-
-performs existing techniques on large programs in terms of bug detection capability, and also achieves
-the highest mean APFD value. The performance demonstrates a growth trend as the size of the program
-increases.</t>
   </si>
   <si>
     <t>V Garousi, R Özkan, A Betin-Can</t>
@@ -4370,7 +4318,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AN203"/>
+  <dimension ref="A1:AN199"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.2">
@@ -9315,47 +9263,47 @@
         <v>2018</v>
       </c>
       <c r="J119" t="s">
-        <v>558</v>
+        <v>981</v>
       </c>
       <c r="AN119" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
     </row>
     <row r="120" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C120" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="D120" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="E120" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="F120">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="J120" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="AN120" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="121" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C121" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="D121" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="E121" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="F121">
         <v>2019</v>
       </c>
       <c r="J121" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="AN121" t="s">
         <v>944</v>
@@ -9363,19 +9311,19 @@
     </row>
     <row r="122" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C122" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="D122" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="E122" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="F122">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="J122" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="AN122" t="s">
         <v>944</v>
@@ -9383,39 +9331,39 @@
     </row>
     <row r="123" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C123" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D123" t="s">
-        <v>967</v>
+        <v>995</v>
       </c>
       <c r="E123" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="F123">
         <v>2013</v>
       </c>
       <c r="J123" t="s">
-        <v>508</v>
+        <v>997</v>
       </c>
       <c r="AN123" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="124" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C124" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="D124" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="E124" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="F124">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="J124" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="AN124" t="s">
         <v>944</v>
@@ -9423,39 +9371,39 @@
     </row>
     <row r="125" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C125" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="D125" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="E125" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="F125">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="J125" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="AN125" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
     </row>
     <row r="126" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C126" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="D126" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="E126" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="F126">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="J126" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="AN126" t="s">
         <v>944</v>
@@ -9463,19 +9411,19 @@
     </row>
     <row r="127" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C127" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="D127" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="E127" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="F127">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="J127" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="AN127" t="s">
         <v>945</v>
@@ -9483,19 +9431,19 @@
     </row>
     <row r="128" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C128" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="D128" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E128" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="F128">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="J128" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="AN128" t="s">
         <v>944</v>
@@ -9503,19 +9451,19 @@
     </row>
     <row r="129" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C129" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="D129" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="E129" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="F129">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="J129" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="AN129" t="s">
         <v>944</v>
@@ -9523,39 +9471,39 @@
     </row>
     <row r="130" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C130" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="D130" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="E130" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="F130">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="J130" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="AN130" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="131" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C131" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="D131" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="E131" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="F131">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="J131" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="AN131" t="s">
         <v>944</v>
@@ -9563,19 +9511,19 @@
     </row>
     <row r="132" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C132" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="D132" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="E132" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="F132">
-        <v>2013</v>
+        <v>2020</v>
       </c>
       <c r="J132" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="AN132" t="s">
         <v>944</v>
@@ -9583,19 +9531,19 @@
     </row>
     <row r="133" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C133" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="D133" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="E133" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="F133">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="J133" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="AN133" t="s">
         <v>944</v>
@@ -9603,19 +9551,19 @@
     </row>
     <row r="134" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C134" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="D134" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="E134" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="F134">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="J134" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="AN134" t="s">
         <v>944</v>
@@ -9623,19 +9571,19 @@
     </row>
     <row r="135" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C135" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="D135" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="E135" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="F135">
         <v>2020</v>
       </c>
       <c r="J135" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="AN135" t="s">
         <v>944</v>
@@ -9643,19 +9591,19 @@
     </row>
     <row r="136" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C136" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="D136" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="E136" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="F136">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="J136" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="AN136" t="s">
         <v>944</v>
@@ -9663,19 +9611,19 @@
     </row>
     <row r="137" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C137" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="D137" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="E137" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="F137">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="J137" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="AN137" t="s">
         <v>944</v>
@@ -9683,19 +9631,19 @@
     </row>
     <row r="138" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C138" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="D138" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="E138" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="F138">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="J138" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="AN138" t="s">
         <v>944</v>
@@ -9703,19 +9651,19 @@
     </row>
     <row r="139" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C139" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="D139" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="E139" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="F139">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="J139" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="AN139" t="s">
         <v>944</v>
@@ -9723,19 +9671,19 @@
     </row>
     <row r="140" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C140" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="D140" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="E140" t="s">
-        <v>357</v>
+        <v>1064</v>
       </c>
       <c r="F140">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="J140" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="AN140" t="s">
         <v>944</v>
@@ -9743,19 +9691,19 @@
     </row>
     <row r="141" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C141" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="D141" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="E141" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="F141">
         <v>2018</v>
       </c>
       <c r="J141" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="AN141" t="s">
         <v>944</v>
@@ -9763,19 +9711,19 @@
     </row>
     <row r="142" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C142" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="D142" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="E142" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="F142">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="J142" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="AN142" t="s">
         <v>944</v>
@@ -9783,19 +9731,19 @@
     </row>
     <row r="143" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C143" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="D143" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="E143" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="F143">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="J143" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="AN143" t="s">
         <v>944</v>
@@ -9803,19 +9751,19 @@
     </row>
     <row r="144" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C144" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="D144" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="E144" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="F144">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="J144" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="AN144" t="s">
         <v>944</v>
@@ -9823,19 +9771,19 @@
     </row>
     <row r="145" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C145" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="D145" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="E145" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="F145">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="J145" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="AN145" t="s">
         <v>944</v>
@@ -9843,19 +9791,19 @@
     </row>
     <row r="146" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C146" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="D146" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="E146" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="F146">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="J146" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="AN146" t="s">
         <v>944</v>
@@ -9863,19 +9811,19 @@
     </row>
     <row r="147" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C147" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="D147" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="E147" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="F147">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="J147" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="AN147" t="s">
         <v>944</v>
@@ -9883,19 +9831,19 @@
     </row>
     <row r="148" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C148" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="D148" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="E148" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="F148">
         <v>2014</v>
       </c>
       <c r="J148" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="AN148" t="s">
         <v>944</v>
@@ -9903,19 +9851,19 @@
     </row>
     <row r="149" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C149" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="D149" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="E149" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="F149">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="J149" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="AN149" t="s">
         <v>944</v>
@@ -9923,19 +9871,19 @@
     </row>
     <row r="150" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C150" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="D150" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="E150" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="F150">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="J150" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="AN150" t="s">
         <v>944</v>
@@ -9943,19 +9891,19 @@
     </row>
     <row r="151" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C151" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="D151" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="E151" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="F151">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="J151" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="AN151" t="s">
         <v>944</v>
@@ -9963,19 +9911,19 @@
     </row>
     <row r="152" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C152" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="D152" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="E152" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="F152">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="J152" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="AN152" t="s">
         <v>944</v>
@@ -9983,19 +9931,19 @@
     </row>
     <row r="153" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C153" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="D153" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
       <c r="E153" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="F153">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="J153" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="AN153" t="s">
         <v>944</v>
@@ -10003,19 +9951,19 @@
     </row>
     <row r="154" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C154" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="D154" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="E154" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="F154">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="J154" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="AN154" t="s">
         <v>944</v>
@@ -10023,19 +9971,19 @@
     </row>
     <row r="155" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C155" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D155" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="E155" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="F155">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="J155" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
       <c r="AN155" t="s">
         <v>944</v>
@@ -10043,19 +9991,19 @@
     </row>
     <row r="156" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C156" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="D156" t="s">
-        <v>1123</v>
+        <v>1027</v>
       </c>
       <c r="E156" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="F156">
-        <v>2024</v>
+        <v>2015</v>
       </c>
       <c r="J156" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="AN156" t="s">
         <v>944</v>
@@ -10063,19 +10011,19 @@
     </row>
     <row r="157" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C157" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="D157" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="E157" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="F157">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="J157" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="AN157" t="s">
         <v>944</v>
@@ -10083,19 +10031,19 @@
     </row>
     <row r="158" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C158" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
       <c r="D158" t="s">
-        <v>1131</v>
+        <v>1027</v>
       </c>
       <c r="E158" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="F158">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="J158" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="AN158" t="s">
         <v>944</v>
@@ -10103,19 +10051,19 @@
     </row>
     <row r="159" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C159" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="D159" t="s">
-        <v>1135</v>
+        <v>1027</v>
       </c>
       <c r="E159" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="F159">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="J159" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="AN159" t="s">
         <v>944</v>
@@ -10123,19 +10071,19 @@
     </row>
     <row r="160" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C160" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="D160" t="s">
-        <v>1036</v>
+        <v>1140</v>
       </c>
       <c r="E160" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="F160">
-        <v>2015</v>
+        <v>2024</v>
       </c>
       <c r="J160" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="AN160" t="s">
         <v>944</v>
@@ -10143,19 +10091,19 @@
     </row>
     <row r="161" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C161" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="D161" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="E161" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="F161">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="J161" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="AN161" t="s">
         <v>944</v>
@@ -10163,19 +10111,19 @@
     </row>
     <row r="162" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C162" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="D162" t="s">
-        <v>1036</v>
+        <v>1148</v>
       </c>
       <c r="E162" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
       <c r="F162">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="J162" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
       <c r="AN162" t="s">
         <v>944</v>
@@ -10183,19 +10131,19 @@
     </row>
     <row r="163" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C163" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="D163" t="s">
-        <v>1036</v>
+        <v>991</v>
       </c>
       <c r="E163" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
       <c r="F163">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="J163" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
       <c r="AN163" t="s">
         <v>944</v>
@@ -10203,19 +10151,19 @@
     </row>
     <row r="164" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C164" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="D164" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="E164" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="F164">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="J164" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="AN164" t="s">
         <v>944</v>
@@ -10223,19 +10171,19 @@
     </row>
     <row r="165" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C165" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
       <c r="D165" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="E165" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="F165">
         <v>2015</v>
       </c>
       <c r="J165" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="AN165" t="s">
         <v>944</v>
@@ -10243,19 +10191,19 @@
     </row>
     <row r="166" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C166" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
       <c r="D166" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
       <c r="E166" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="F166">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="J166" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
       <c r="AN166" t="s">
         <v>944</v>
@@ -10263,39 +10211,39 @@
     </row>
     <row r="167" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C167" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
       <c r="D167" t="s">
-        <v>996</v>
+        <v>1130</v>
       </c>
       <c r="E167" t="s">
-        <v>1164</v>
+        <v>1167</v>
       </c>
       <c r="F167">
         <v>2016</v>
       </c>
       <c r="J167" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
       <c r="AN167" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="168" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C168" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
       <c r="D168" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
       <c r="E168" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="F168">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="J168" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="AN168" t="s">
         <v>944</v>
@@ -10303,19 +10251,19 @@
     </row>
     <row r="169" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C169" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
       <c r="D169" t="s">
-        <v>1171</v>
+        <v>816</v>
       </c>
       <c r="E169" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="F169">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="J169" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="AN169" t="s">
         <v>944</v>
@@ -10323,19 +10271,19 @@
     </row>
     <row r="170" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C170" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="D170" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="E170" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="F170">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="J170" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="AN170" t="s">
         <v>944</v>
@@ -10343,19 +10291,19 @@
     </row>
     <row r="171" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C171" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="D171" t="s">
-        <v>1142</v>
+        <v>1181</v>
       </c>
       <c r="E171" t="s">
-        <v>1179</v>
+        <v>1182</v>
       </c>
       <c r="F171">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="J171" t="s">
-        <v>1180</v>
+        <v>1183</v>
       </c>
       <c r="AN171" t="s">
         <v>943</v>
@@ -10363,19 +10311,19 @@
     </row>
     <row r="172" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C172" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="D172" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="E172" t="s">
-        <v>1183</v>
+        <v>1186</v>
       </c>
       <c r="F172">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="J172" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="AN172" t="s">
         <v>944</v>
@@ -10383,19 +10331,19 @@
     </row>
     <row r="173" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C173" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="D173" t="s">
-        <v>816</v>
+        <v>1189</v>
       </c>
       <c r="E173" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="F173">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="J173" t="s">
-        <v>1187</v>
+        <v>1191</v>
       </c>
       <c r="AN173" t="s">
         <v>944</v>
@@ -10403,19 +10351,19 @@
     </row>
     <row r="174" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C174" t="s">
-        <v>1188</v>
+        <v>1192</v>
       </c>
       <c r="D174" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="E174" t="s">
-        <v>1190</v>
+        <v>1194</v>
       </c>
       <c r="F174">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="J174" t="s">
-        <v>1191</v>
+        <v>1195</v>
       </c>
       <c r="AN174" t="s">
         <v>944</v>
@@ -10423,39 +10371,39 @@
     </row>
     <row r="175" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C175" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="D175" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
       <c r="E175" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="F175">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="J175" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="AN175" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="176" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C176" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="D176" t="s">
-        <v>1197</v>
+        <v>1201</v>
       </c>
       <c r="E176" t="s">
-        <v>1198</v>
+        <v>1202</v>
       </c>
       <c r="F176">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="J176" t="s">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="AN176" t="s">
         <v>944</v>
@@ -10463,79 +10411,79 @@
     </row>
     <row r="177" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C177" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="D177" t="s">
-        <v>1201</v>
+        <v>1205</v>
       </c>
       <c r="E177" t="s">
-        <v>1202</v>
+        <v>1206</v>
       </c>
       <c r="F177">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="J177" t="s">
-        <v>1203</v>
+        <v>1207</v>
       </c>
       <c r="AN177" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="178" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C178" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
       <c r="D178" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
       <c r="E178" t="s">
-        <v>1206</v>
+        <v>1210</v>
       </c>
       <c r="F178">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="J178" t="s">
-        <v>1207</v>
+        <v>1211</v>
       </c>
       <c r="AN178" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="179" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C179" t="s">
-        <v>1208</v>
+        <v>1212</v>
       </c>
       <c r="D179" t="s">
-        <v>1209</v>
+        <v>1213</v>
       </c>
       <c r="E179" t="s">
-        <v>1210</v>
+        <v>1214</v>
       </c>
       <c r="F179">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="J179" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="AN179" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="180" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C180" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="D180" t="s">
-        <v>1213</v>
+        <v>1217</v>
       </c>
       <c r="E180" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="F180">
-        <v>2017</v>
+        <v>2024</v>
       </c>
       <c r="J180" t="s">
-        <v>1215</v>
+        <v>1219</v>
       </c>
       <c r="AN180" t="s">
         <v>944</v>
@@ -10543,79 +10491,79 @@
     </row>
     <row r="181" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C181" t="s">
-        <v>1216</v>
+        <v>1220</v>
       </c>
       <c r="D181" t="s">
-        <v>1217</v>
+        <v>1221</v>
       </c>
       <c r="E181" t="s">
-        <v>1218</v>
+        <v>1222</v>
       </c>
       <c r="F181">
         <v>2021</v>
       </c>
       <c r="J181" t="s">
-        <v>1219</v>
+        <v>1223</v>
       </c>
       <c r="AN181" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="182" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C182" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D182" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="E182" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
       <c r="F182">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="J182" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="AN182" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="183" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C183" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
       <c r="D183" t="s">
-        <v>1225</v>
+        <v>1229</v>
       </c>
       <c r="E183" t="s">
-        <v>1226</v>
+        <v>1230</v>
       </c>
       <c r="F183">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="J183" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
       <c r="AN183" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="184" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C184" t="s">
-        <v>1228</v>
+        <v>1232</v>
       </c>
       <c r="D184" t="s">
-        <v>1229</v>
+        <v>1233</v>
       </c>
       <c r="E184" t="s">
-        <v>1230</v>
+        <v>1234</v>
       </c>
       <c r="F184">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="J184" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="AN184" t="s">
         <v>944</v>
@@ -10623,19 +10571,19 @@
     </row>
     <row r="185" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C185" t="s">
-        <v>1232</v>
+        <v>1236</v>
       </c>
       <c r="D185" t="s">
-        <v>1233</v>
+        <v>1237</v>
       </c>
       <c r="E185" t="s">
-        <v>1234</v>
+        <v>1238</v>
       </c>
       <c r="F185">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J185" t="s">
-        <v>1235</v>
+        <v>1239</v>
       </c>
       <c r="AN185" t="s">
         <v>944</v>
@@ -10643,19 +10591,19 @@
     </row>
     <row r="186" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C186" t="s">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="D186" t="s">
-        <v>1237</v>
+        <v>1241</v>
       </c>
       <c r="E186" t="s">
-        <v>1238</v>
+        <v>1242</v>
       </c>
       <c r="F186">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="J186" t="s">
-        <v>1239</v>
+        <v>1243</v>
       </c>
       <c r="AN186" t="s">
         <v>944</v>
@@ -10663,19 +10611,19 @@
     </row>
     <row r="187" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C187" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
       <c r="D187" t="s">
-        <v>1241</v>
+        <v>1245</v>
       </c>
       <c r="E187" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="F187">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="J187" t="s">
-        <v>1243</v>
+        <v>1247</v>
       </c>
       <c r="AN187" t="s">
         <v>944</v>
@@ -10683,19 +10631,19 @@
     </row>
     <row r="188" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C188" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="D188" t="s">
-        <v>1245</v>
+        <v>1249</v>
       </c>
       <c r="E188" t="s">
-        <v>1246</v>
+        <v>1250</v>
       </c>
       <c r="F188">
         <v>2022</v>
       </c>
       <c r="J188" t="s">
-        <v>1247</v>
+        <v>1251</v>
       </c>
       <c r="AN188" t="s">
         <v>944</v>
@@ -10703,19 +10651,19 @@
     </row>
     <row r="189" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C189" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="D189" t="s">
-        <v>1249</v>
+        <v>1253</v>
       </c>
       <c r="E189" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="F189">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J189" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="AN189" t="s">
         <v>944</v>
@@ -10723,19 +10671,19 @@
     </row>
     <row r="190" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C190" t="s">
-        <v>1252</v>
+        <v>1256</v>
       </c>
       <c r="D190" t="s">
-        <v>1253</v>
+        <v>1257</v>
       </c>
       <c r="E190" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="F190">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J190" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="AN190" t="s">
         <v>944</v>
@@ -10743,39 +10691,39 @@
     </row>
     <row r="191" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C191" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="D191" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="E191" t="s">
-        <v>1258</v>
+        <v>1262</v>
       </c>
       <c r="F191">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="J191" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="AN191" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="192" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C192" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="D192" t="s">
-        <v>1261</v>
+        <v>1253</v>
       </c>
       <c r="E192" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="F192">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J192" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="AN192" t="s">
         <v>944</v>
@@ -10783,19 +10731,19 @@
     </row>
     <row r="193" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C193" t="s">
-        <v>1264</v>
+        <v>1267</v>
       </c>
       <c r="D193" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="E193" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="F193">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="J193" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="AN193" t="s">
         <v>944</v>
@@ -10803,19 +10751,19 @@
     </row>
     <row r="194" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C194" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="D194" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="E194" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="F194">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="J194" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="AN194" t="s">
         <v>944</v>
@@ -10823,39 +10771,36 @@
     </row>
     <row r="195" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C195" t="s">
-        <v>1272</v>
-      </c>
-      <c r="D195" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="E195" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="F195">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="J195" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="AN195" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
     </row>
     <row r="196" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C196" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="D196" t="s">
-        <v>1265</v>
+        <v>1279</v>
       </c>
       <c r="E196" t="s">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="F196">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="J196" t="s">
-        <v>1278</v>
+        <v>1281</v>
       </c>
       <c r="AN196" t="s">
         <v>944</v>
@@ -10863,138 +10808,61 @@
     </row>
     <row r="197" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C197" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
       <c r="D197" t="s">
-        <v>1280</v>
+        <v>1027</v>
       </c>
       <c r="E197" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="F197">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="J197" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="AN197" t="s">
         <v>944</v>
       </c>
     </row>
-    <row r="198" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="198" spans="3:40" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C198" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="D198" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="E198" t="s">
         <v>1285</v>
       </c>
       <c r="F198">
-        <v>2022</v>
-      </c>
-      <c r="J198" t="s">
-        <v>1286</v>
+        <v>2020</v>
+      </c>
+      <c r="J198" s="3" t="s">
+        <v>1288</v>
       </c>
       <c r="AN198" t="s">
         <v>944</v>
       </c>
     </row>
-    <row r="199" spans="3:40" x14ac:dyDescent="0.2">
-      <c r="C199" t="s">
-        <v>1287</v>
+    <row r="199" spans="3:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C199" s="3" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D199" t="s">
+        <v>816</v>
       </c>
       <c r="E199" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F199">
-        <v>2025</v>
+        <v>2015</v>
       </c>
       <c r="J199" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="AN199" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="200" spans="3:40" x14ac:dyDescent="0.2">
-      <c r="C200" t="s">
-        <v>1290</v>
-      </c>
-      <c r="D200" t="s">
-        <v>1291</v>
-      </c>
-      <c r="E200" t="s">
-        <v>1292</v>
-      </c>
-      <c r="F200">
-        <v>2024</v>
-      </c>
-      <c r="J200" t="s">
-        <v>1293</v>
-      </c>
-      <c r="AN200" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="201" spans="3:40" x14ac:dyDescent="0.2">
-      <c r="C201" t="s">
-        <v>1295</v>
-      </c>
-      <c r="D201" t="s">
-        <v>1036</v>
-      </c>
-      <c r="E201" t="s">
-        <v>1294</v>
-      </c>
-      <c r="F201">
-        <v>2024</v>
-      </c>
-      <c r="J201" t="s">
-        <v>1296</v>
-      </c>
-      <c r="AN201" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="202" spans="3:40" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C202" t="s">
-        <v>1298</v>
-      </c>
-      <c r="D202" t="s">
-        <v>1299</v>
-      </c>
-      <c r="E202" t="s">
-        <v>1297</v>
-      </c>
-      <c r="F202">
-        <v>2020</v>
-      </c>
-      <c r="J202" s="3" t="s">
-        <v>1300</v>
-      </c>
-      <c r="AN202" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="203" spans="3:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C203" s="3" t="s">
-        <v>1302</v>
-      </c>
-      <c r="D203" t="s">
-        <v>816</v>
-      </c>
-      <c r="E203" t="s">
-        <v>1301</v>
-      </c>
-      <c r="F203">
-        <v>2015</v>
-      </c>
-      <c r="J203" t="s">
-        <v>1303</v>
-      </c>
-      <c r="AN203" t="s">
         <v>944</v>
       </c>
     </row>
@@ -11027,6 +10895,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B6889C2593FACB4192549183B8B19287" ma:contentTypeVersion="11" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="8f919e2780f892880bff7efb43d3db1d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ab92c565-5003-4ac3-93a3-a3ce8796a3c0" xmlns:ns3="aa1b21cb-23df-461b-8b8e-4aaeac2f3f50" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1ca4d89da73e1329ebe7ff2e4ed471c6" ns2:_="" ns3:_="">
     <xsd:import namespace="ab92c565-5003-4ac3-93a3-a3ce8796a3c0"/>
@@ -11221,15 +11098,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11242,13 +11110,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99CBEF94-1D47-48BE-AD33-518B5390AF03}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C54EB65-76B8-485C-95C9-FDA0BA22D9B0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C54EB65-76B8-485C-95C9-FDA0BA22D9B0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99CBEF94-1D47-48BE-AD33-518B5390AF03}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="ab92c565-5003-4ac3-93a3-a3ce8796a3c0"/>
+    <ds:schemaRef ds:uri="aa1b21cb-23df-461b-8b8e-4aaeac2f3f50"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8819F48-7B72-43AF-AD68-E89993DDD9B1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8819F48-7B72-43AF-AD68-E89993DDD9B1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ab92c565-5003-4ac3-93a3-a3ce8796a3c0"/>
+    <ds:schemaRef ds:uri="aa1b21cb-23df-461b-8b8e-4aaeac2f3f50"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>